--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.47055276937438</v>
+        <v>5.113964825023337</v>
       </c>
       <c r="D2" t="n">
-        <v>32.03344764218602</v>
+        <v>5.205435241855228</v>
       </c>
       <c r="E2" t="n">
-        <v>4.222969686707424</v>
+        <v>0.6862325740899566</v>
       </c>
       <c r="F2" t="n">
-        <v>4.588389877634368</v>
+        <v>0.7456133551155846</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.02461339595953</v>
+        <v>3.741499676843424</v>
       </c>
       <c r="D3" t="n">
-        <v>22.85666788691728</v>
+        <v>3.714208531624059</v>
       </c>
       <c r="E3" t="n">
-        <v>4.222969686707424</v>
+        <v>0.6862325740899566</v>
       </c>
       <c r="F3" t="n">
-        <v>4.588389877634368</v>
+        <v>0.7456133551155846</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
